--- a/output/2026-08-31_23_Italia_Liguria_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-08-31_23_Italia_Liguria_Impiantistica_aspirazione_industriale.xlsx
@@ -536,10 +536,9 @@
           <t>010 566193</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Azienda generalista HVAC dal 1984, Daikin Comfort Store; aspirazione confermata come una delle attivita' ma non esclusiva. Indirizzo confermato (Via Rimassa 172/R).</t>
+          <t>Azienda generalista HVAC dal 1984, Daikin Comfort Store; aspirazione confermata come una delle attivita' ma non esclusiva. Indirizzo confermato (Via Rimassa 172/R). [DUPLICATO — vedi anche: 2026-08-31_22_Italia_Liguria_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -616,7 +615,6 @@
           <t>0187 926383</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Azienda reale e ben documentata (dal 2003), collabora con enti pubblici Liguria/Toscana. ATTENZIONE modello di business: servizio di aspirazione con mezzo mobile, non progettazione/installazione di impianti fissi - valutare fit rispetto al target 'impiantistica'.</t>
@@ -696,7 +694,6 @@
           <t>019 680620</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>P.IVA 01567360092. Aspirazione polveri confermata come una delle attivita' offerte, ma azienda generalista (elettrico, idraulico, VMC, fotovoltaico).</t>
@@ -741,7 +738,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Azienda storica (oltre 40 anni), ~100 addetti, contatti pienamente confermati da fonte terza indipendente. Modello di business: servizi di aspirazione/pulizia industriale conto terzi, non progettazione impianti fissi.</t>
+          <t>Azienda storica (oltre 40 anni), ~100 addetti, contatti pienamente confermati da fonte terza indipendente. Modello di business: servizi di aspirazione/pulizia industriale conto terzi, non progettazione impianti fissi. [DUPLICATO — vedi anche: 2026-08-31_22_Italia_Liguria_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -783,7 +780,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Telefono confermato da fonte terza. Esiste anche dominio ufficiale alternativo idroservice-sas.it. Settore affine (nebulizzazione/abbattimento polveri e macchine di pulizia), non impiantistica fissa di aspirazione industriale.</t>
+          <t>Telefono confermato da fonte terza. Esiste anche dominio ufficiale alternativo idroservice-sas.it. Settore affine (nebulizzazione/abbattimento polveri e macchine di pulizia), non impiantistica fissa di aspirazione industriale. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">

--- a/output/2026-08-31_23_Italia_Liguria_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-08-31_23_Italia_Liguria_Impiantistica_aspirazione_industriale.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
